--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/2206-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/2206-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2765042-6F7F-434A-893E-D04CC66C9862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B403533F-6C2D-416F-934B-258670C00BA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{4B1B6200-5455-4E63-9BEE-F1C5CCDF0138}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{6386AF55-EE78-4EA3-A8D2-3ED8A48A48FF}"/>
   </bookViews>
   <sheets>
     <sheet name="2206-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1487,23 +1487,22 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30AEA05B-37B5-4B3B-AE4B-EDAF695CD79A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5C00074-7A7F-43CF-BFD1-EC49334C7799}">
   <dimension ref="A1:R58"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.5546875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="18" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1531,7 +1530,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1561,7 +1560,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1607,7 +1606,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1657,7 +1656,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2026</v>
       </c>
@@ -1711,7 +1710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>26</v>
       </c>
@@ -1767,7 +1766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="39">
         <v>2025</v>
       </c>
@@ -1821,7 +1820,7 @@
         <v>4.7300000000000004</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
         <v>26</v>
       </c>
@@ -1877,7 +1876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>26</v>
       </c>
@@ -1933,7 +1932,7 @@
         <v>4.7300000000000004</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>26</v>
       </c>
@@ -1989,7 +1988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="37">
         <v>2024</v>
       </c>
@@ -2043,7 +2042,7 @@
         <v>3.84</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>26</v>
       </c>
@@ -2099,7 +2098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>26</v>
       </c>
@@ -2155,7 +2154,7 @@
         <v>3.84</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>26</v>
       </c>
@@ -2211,7 +2210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="39">
         <v>2023</v>
       </c>
@@ -2265,7 +2264,7 @@
         <v>2.33</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>26</v>
       </c>
@@ -2321,7 +2320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
         <v>26</v>
       </c>
@@ -2377,7 +2376,7 @@
         <v>2.33</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="17" t="s">
         <v>26</v>
       </c>
@@ -2433,7 +2432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="37">
         <v>2022</v>
       </c>
@@ -2487,7 +2486,7 @@
         <v>3.54</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>26</v>
       </c>
@@ -2543,7 +2542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>26</v>
       </c>
@@ -2599,7 +2598,7 @@
         <v>3.54</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
         <v>26</v>
       </c>
@@ -2655,7 +2654,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="39">
         <v>2021</v>
       </c>
@@ -2709,7 +2708,7 @@
         <v>4.55</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
         <v>26</v>
       </c>
@@ -2765,7 +2764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
         <v>26</v>
       </c>
@@ -2821,7 +2820,7 @@
         <v>4.55</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="17" t="s">
         <v>26</v>
       </c>
@@ -2877,7 +2876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="37">
         <v>2020</v>
       </c>
@@ -2931,7 +2930,7 @@
         <v>4.67</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
         <v>26</v>
       </c>
@@ -2987,7 +2986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
         <v>26</v>
       </c>
@@ -3043,7 +3042,7 @@
         <v>4.67</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="39">
         <v>2019</v>
       </c>
@@ -3097,7 +3096,7 @@
         <v>4.43</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
         <v>26</v>
       </c>
@@ -3153,7 +3152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="17" t="s">
         <v>26</v>
       </c>
@@ -3209,7 +3208,7 @@
         <v>4.43</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="37">
         <v>2018</v>
       </c>
@@ -3263,7 +3262,7 @@
         <v>4.6900000000000004</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="39">
         <v>2017</v>
       </c>
@@ -3317,7 +3316,7 @@
         <v>4.92</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="37">
         <v>2016</v>
       </c>
@@ -3371,7 +3370,7 @@
         <v>4.4400000000000004</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="39">
         <v>2015</v>
       </c>
@@ -3425,7 +3424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="37">
         <v>2014</v>
       </c>
@@ -3479,7 +3478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="39">
         <v>2013</v>
       </c>
@@ -3533,7 +3532,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="37">
         <v>2011</v>
       </c>
@@ -3587,7 +3586,7 @@
         <v>3.78</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="39">
         <v>2010</v>
       </c>
@@ -3641,7 +3640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="37">
         <v>2009</v>
       </c>
@@ -3695,7 +3694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="39">
         <v>2008</v>
       </c>
@@ -3749,7 +3748,7 @@
         <v>8.18</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="37">
         <v>2007</v>
       </c>
@@ -3803,7 +3802,7 @@
         <v>3.98</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="39">
         <v>2006</v>
       </c>
@@ -3857,7 +3856,7 @@
         <v>6.13</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="37">
         <v>2005</v>
       </c>
@@ -3911,7 +3910,7 @@
         <v>9.2799999999999994</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="39">
         <v>2004</v>
       </c>
@@ -3965,7 +3964,7 @@
         <v>4.97</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="37">
         <v>2003</v>
       </c>
@@ -4019,7 +4018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="39">
         <v>2002</v>
       </c>
@@ -4073,7 +4072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="37">
         <v>2001</v>
       </c>
@@ -4127,7 +4126,7 @@
         <v>9.5500000000000007</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="39">
         <v>2000</v>
       </c>
@@ -4181,7 +4180,7 @@
         <v>9.3800000000000008</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="37">
         <v>1999</v>
       </c>
@@ -4235,7 +4234,7 @@
         <v>5.83</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="39">
         <v>1998</v>
       </c>
@@ -4289,7 +4288,7 @@
         <v>3.77</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="37">
         <v>1997</v>
       </c>
@@ -4343,7 +4342,7 @@
         <v>2.46</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="39">
         <v>1996</v>
       </c>
@@ -4397,7 +4396,7 @@
         <v>3.65</v>
       </c>
     </row>
-    <row r="55" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="37">
         <v>1995</v>
       </c>
@@ -4451,7 +4450,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="56" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="39">
         <v>1994</v>
       </c>
@@ -4505,7 +4504,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="57" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="37">
         <v>1993</v>
       </c>
@@ -4559,7 +4558,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="58" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="39" t="s">
         <v>48</v>
       </c>
